--- a/Advance Excel/Day01_ Practise.xlsx
+++ b/Advance Excel/Day01_ Practise.xlsx
@@ -4261,7 +4261,7 @@
         <v>0</v>
       </c>
       <c r="V67" t="str">
-        <f t="shared" ref="V67:V98" si="11">IF(E67&gt;=8000,"10000",IF(E67&gt;=5000,"5000",IF(E67&lt;5000,"0")))</f>
+        <f t="shared" ref="V67:V102" si="11">IF(E67&gt;=8000,"10000",IF(E67&gt;=5000,"5000",IF(E67&lt;5000,"0")))</f>
         <v>5000</v>
       </c>
     </row>
@@ -5733,7 +5733,7 @@
         <v>0</v>
       </c>
       <c r="V99" t="str">
-        <f>IF(E99&gt;=8000,"10000",IF(E99&gt;=5000,"5000",IF(E99&lt;5000,"0")))</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -5779,7 +5779,7 @@
         <v>0</v>
       </c>
       <c r="V100" t="str">
-        <f>IF(E100&gt;=8000,"10000",IF(E100&gt;=5000,"5000",IF(E100&lt;5000,"0")))</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -5825,7 +5825,7 @@
         <v>0</v>
       </c>
       <c r="V101" t="str">
-        <f>IF(E101&gt;=8000,"10000",IF(E101&gt;=5000,"5000",IF(E101&lt;5000,"0")))</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -5843,7 +5843,7 @@
         <v>no salary</v>
       </c>
       <c r="V102" t="str">
-        <f>IF(E102&gt;=8000,"10000",IF(E102&gt;=5000,"5000",IF(E102&lt;5000,"0")))</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
